--- a/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA69C66-7059-4EC4-80FE-68D2A263DCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F80A0A4-6952-4D89-A77B-CFF9F2FD1A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="374">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1307,6 +1307,21 @@
   </si>
   <si>
     <t>kWh_th</t>
+  </si>
+  <si>
+    <t>Verkaufspreiseanalyse</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis Bilanznull</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>Verkaufspreis Bilanznull mit Vorverkauf</t>
+  </si>
+  <si>
+    <t>calc_price</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1527,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1636,35 +1651,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1673,13 +1673,34 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3406,7 +3427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -3439,10 +3460,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3457,7 +3478,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="88"/>
+      <c r="A3" s="84"/>
       <c r="B3" s="80"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
@@ -3471,7 +3492,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
+      <c r="A4" s="84"/>
       <c r="B4" s="80"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3485,7 +3506,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="88"/>
+      <c r="A5" s="84"/>
       <c r="B5" s="80"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
@@ -3499,7 +3520,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
+      <c r="A6" s="84"/>
       <c r="B6" s="80"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
@@ -3513,7 +3534,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
+      <c r="A7" s="84"/>
       <c r="B7" s="80"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
@@ -3527,7 +3548,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
+      <c r="A8" s="84"/>
       <c r="B8" s="80"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
@@ -3541,7 +3562,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
+      <c r="A9" s="84"/>
       <c r="B9" s="80"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
@@ -3555,7 +3576,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="80"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
@@ -3569,13 +3590,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="80"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="83" t="s">
+      <c r="A12" s="84"/>
+      <c r="B12" s="86" t="s">
         <v>232</v>
       </c>
       <c r="C12" s="48" t="s">
@@ -3590,8 +3611,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="45" t="s">
         <v>261</v>
       </c>
@@ -3604,8 +3625,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="45" t="s">
         <v>140</v>
       </c>
@@ -3618,8 +3639,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="45" t="s">
         <v>262</v>
       </c>
@@ -3632,8 +3653,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="88"/>
-      <c r="B16" s="84"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
       <c r="C16" s="45" t="s">
         <v>84</v>
       </c>
@@ -3646,8 +3667,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
-      <c r="B17" s="84"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="45" t="s">
         <v>142</v>
       </c>
@@ -3660,8 +3681,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
-      <c r="B18" s="84"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="87"/>
       <c r="C18" s="45" t="s">
         <v>156</v>
       </c>
@@ -3674,8 +3695,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="84"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="87"/>
       <c r="C19" s="45" t="s">
         <v>198</v>
       </c>
@@ -3688,8 +3709,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="84"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="87"/>
       <c r="C20" s="45" t="s">
         <v>168</v>
       </c>
@@ -3702,8 +3723,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="84"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="87"/>
       <c r="C21" s="45" t="s">
         <v>190</v>
       </c>
@@ -3716,16 +3737,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="93"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="88"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="53"/>
       <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="83" t="s">
+      <c r="A23" s="84"/>
+      <c r="B23" s="86" t="s">
         <v>297</v>
       </c>
       <c r="C23" s="45" t="s">
@@ -3740,8 +3761,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="84"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="45" t="s">
         <v>108</v>
       </c>
@@ -3754,8 +3775,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="84"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="87"/>
       <c r="C25" s="45" t="s">
         <v>84</v>
       </c>
@@ -3768,8 +3789,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="84"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="87"/>
       <c r="C26" s="45" t="s">
         <v>320</v>
       </c>
@@ -3782,8 +3803,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="84"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="87"/>
       <c r="C27" s="45" t="s">
         <v>142</v>
       </c>
@@ -3796,8 +3817,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
-      <c r="B28" s="84"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="87"/>
       <c r="C28" s="45" t="s">
         <v>156</v>
       </c>
@@ -3810,8 +3831,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
-      <c r="B29" s="84"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="87"/>
       <c r="C29" s="45" t="s">
         <v>198</v>
       </c>
@@ -3824,8 +3845,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="88"/>
-      <c r="B30" s="84"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="87"/>
       <c r="C30" s="45" t="s">
         <v>168</v>
       </c>
@@ -3838,8 +3859,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="88"/>
-      <c r="B31" s="84"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="87"/>
       <c r="C31" s="45" t="s">
         <v>190</v>
       </c>
@@ -3852,16 +3873,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="88"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="88"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52"/>
       <c r="E32" s="53"/>
       <c r="F32" s="52"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="88"/>
-      <c r="B33" s="94" t="s">
+      <c r="A33" s="84"/>
+      <c r="B33" s="89" t="s">
         <v>231</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -3876,8 +3897,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="88"/>
-      <c r="B34" s="94"/>
+      <c r="A34" s="84"/>
+      <c r="B34" s="89"/>
       <c r="C34" s="45" t="s">
         <v>108</v>
       </c>
@@ -3890,8 +3911,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="88"/>
-      <c r="B35" s="94"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="45" t="s">
         <v>84</v>
       </c>
@@ -3904,8 +3925,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
-      <c r="B36" s="94"/>
+      <c r="A36" s="84"/>
+      <c r="B36" s="89"/>
       <c r="C36" s="45" t="s">
         <v>307</v>
       </c>
@@ -3918,8 +3939,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
-      <c r="B37" s="94"/>
+      <c r="A37" s="84"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="45" t="s">
         <v>274</v>
       </c>
@@ -3932,8 +3953,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
-      <c r="B38" s="94"/>
+      <c r="A38" s="84"/>
+      <c r="B38" s="89"/>
       <c r="C38" s="45" t="s">
         <v>142</v>
       </c>
@@ -3946,8 +3967,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
-      <c r="B39" s="94"/>
+      <c r="A39" s="84"/>
+      <c r="B39" s="89"/>
       <c r="C39" s="45" t="s">
         <v>156</v>
       </c>
@@ -3960,8 +3981,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="88"/>
-      <c r="B40" s="94"/>
+      <c r="A40" s="84"/>
+      <c r="B40" s="89"/>
       <c r="C40" s="45" t="s">
         <v>198</v>
       </c>
@@ -3974,8 +3995,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="88"/>
-      <c r="B41" s="94"/>
+      <c r="A41" s="84"/>
+      <c r="B41" s="89"/>
       <c r="C41" s="45" t="s">
         <v>168</v>
       </c>
@@ -3988,8 +4009,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
-      <c r="B42" s="94"/>
+      <c r="A42" s="84"/>
+      <c r="B42" s="89"/>
       <c r="C42" s="45" t="s">
         <v>190</v>
       </c>
@@ -4002,18 +4023,18 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="88"/>
-      <c r="B43" s="94"/>
+      <c r="A43" s="84"/>
+      <c r="B43" s="89"/>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
       <c r="E43" s="50"/>
       <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="87" t="s">
+      <c r="A44" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="96" t="s">
+      <c r="B44" s="93" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="26" t="s">
@@ -4028,7 +4049,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="88"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="82"/>
       <c r="C45" s="13" t="s">
         <v>112</v>
@@ -4042,7 +4063,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="82"/>
       <c r="C46" s="13" t="s">
         <v>136</v>
@@ -4056,7 +4077,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="88"/>
+      <c r="A47" s="84"/>
       <c r="B47" s="82"/>
       <c r="C47" s="13" t="s">
         <v>137</v>
@@ -4070,7 +4091,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="88"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="82"/>
       <c r="C48" s="13" t="s">
         <v>142</v>
@@ -4084,7 +4105,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="82"/>
       <c r="C49" s="13" t="s">
         <v>156</v>
@@ -4098,7 +4119,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
+      <c r="A50" s="84"/>
       <c r="B50" s="82"/>
       <c r="C50" s="13" t="s">
         <v>198</v>
@@ -4112,7 +4133,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="88"/>
+      <c r="A51" s="84"/>
       <c r="B51" s="82"/>
       <c r="C51" s="13" t="s">
         <v>168</v>
@@ -4126,7 +4147,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="88"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="82"/>
       <c r="C52" s="13" t="s">
         <v>190</v>
@@ -4140,16 +4161,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="88"/>
-      <c r="B53" s="91"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="94"/>
       <c r="C53" s="37"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
       <c r="F53" s="37"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="88"/>
-      <c r="B54" s="94" t="s">
+      <c r="A54" s="84"/>
+      <c r="B54" s="89" t="s">
         <v>344</v>
       </c>
       <c r="C54" s="45" t="s">
@@ -4164,8 +4185,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="88"/>
-      <c r="B55" s="94"/>
+      <c r="A55" s="84"/>
+      <c r="B55" s="89"/>
       <c r="C55" s="45" t="s">
         <v>112</v>
       </c>
@@ -4178,8 +4199,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="88"/>
-      <c r="B56" s="94"/>
+      <c r="A56" s="84"/>
+      <c r="B56" s="89"/>
       <c r="C56" s="45" t="s">
         <v>136</v>
       </c>
@@ -4192,8 +4213,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="88"/>
-      <c r="B57" s="94"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="89"/>
       <c r="C57" s="45" t="s">
         <v>137</v>
       </c>
@@ -4206,8 +4227,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="88"/>
-      <c r="B58" s="94"/>
+      <c r="A58" s="84"/>
+      <c r="B58" s="89"/>
       <c r="C58" s="45" t="s">
         <v>142</v>
       </c>
@@ -4220,8 +4241,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="94"/>
+      <c r="A59" s="84"/>
+      <c r="B59" s="89"/>
       <c r="C59" s="45" t="s">
         <v>156</v>
       </c>
@@ -4234,8 +4255,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="94"/>
+      <c r="A60" s="84"/>
+      <c r="B60" s="89"/>
       <c r="C60" s="45" t="s">
         <v>198</v>
       </c>
@@ -4248,8 +4269,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="94"/>
+      <c r="A61" s="84"/>
+      <c r="B61" s="89"/>
       <c r="C61" s="45" t="s">
         <v>168</v>
       </c>
@@ -4262,8 +4283,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="94"/>
+      <c r="A62" s="84"/>
+      <c r="B62" s="89"/>
       <c r="C62" s="45" t="s">
         <v>190</v>
       </c>
@@ -4276,16 +4297,16 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
-      <c r="B63" s="97"/>
+      <c r="A63" s="84"/>
+      <c r="B63" s="95"/>
       <c r="C63" s="45"/>
       <c r="D63" s="45"/>
       <c r="E63" s="50"/>
       <c r="F63" s="45"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="90" t="s">
+      <c r="A64" s="84"/>
+      <c r="B64" s="91" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="35" t="s">
@@ -4300,7 +4321,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="82"/>
       <c r="C65" s="13" t="s">
         <v>114</v>
@@ -4314,7 +4335,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
+      <c r="A66" s="84"/>
       <c r="B66" s="80"/>
       <c r="C66" s="13" t="s">
         <v>112</v>
@@ -4328,7 +4349,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="88"/>
+      <c r="A67" s="84"/>
       <c r="B67" s="80"/>
       <c r="C67" s="13" t="s">
         <v>108</v>
@@ -4342,7 +4363,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="88"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="80"/>
       <c r="C68" s="13" t="s">
         <v>127</v>
@@ -4356,7 +4377,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="88"/>
+      <c r="A69" s="84"/>
       <c r="B69" s="80"/>
       <c r="C69" s="13" t="s">
         <v>128</v>
@@ -4370,7 +4391,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="88"/>
+      <c r="A70" s="84"/>
       <c r="B70" s="80"/>
       <c r="C70" s="13" t="s">
         <v>142</v>
@@ -4384,7 +4405,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="88"/>
+      <c r="A71" s="84"/>
       <c r="B71" s="80"/>
       <c r="C71" s="13" t="s">
         <v>156</v>
@@ -4398,7 +4419,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="88"/>
+      <c r="A72" s="84"/>
       <c r="B72" s="80"/>
       <c r="C72" s="13" t="s">
         <v>198</v>
@@ -4412,7 +4433,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="88"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="80"/>
       <c r="C73" s="13" t="s">
         <v>168</v>
@@ -4426,7 +4447,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="88"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="80"/>
       <c r="C74" s="13" t="s">
         <v>190</v>
@@ -4440,18 +4461,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="89"/>
-      <c r="B75" s="95"/>
+      <c r="A75" s="90"/>
+      <c r="B75" s="92"/>
       <c r="C75" s="41"/>
       <c r="D75" s="41"/>
       <c r="E75" s="42"/>
       <c r="F75" s="41"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="87" t="s">
+      <c r="A76" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="86" t="s">
+      <c r="B76" s="85" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="26" t="s">
@@ -4466,7 +4487,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="88"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="80"/>
       <c r="C77" s="13" t="s">
         <v>154</v>
@@ -4480,13 +4501,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="88"/>
+      <c r="A78" s="84"/>
       <c r="B78" s="81"/>
       <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="88"/>
-      <c r="B79" s="90" t="s">
+      <c r="A79" s="84"/>
+      <c r="B79" s="91" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="35" t="s">
@@ -4501,7 +4522,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="88"/>
+      <c r="A80" s="84"/>
       <c r="B80" s="82"/>
       <c r="C80" s="13" t="s">
         <v>108</v>
@@ -4515,7 +4536,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="88"/>
+      <c r="A81" s="84"/>
       <c r="B81" s="82"/>
       <c r="C81" s="13" t="s">
         <v>123</v>
@@ -4529,7 +4550,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="88"/>
+      <c r="A82" s="84"/>
       <c r="B82" s="82"/>
       <c r="C82" s="13" t="s">
         <v>142</v>
@@ -4543,7 +4564,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="88"/>
+      <c r="A83" s="84"/>
       <c r="B83" s="82"/>
       <c r="C83" s="13" t="s">
         <v>156</v>
@@ -4557,7 +4578,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="88"/>
+      <c r="A84" s="84"/>
       <c r="B84" s="82"/>
       <c r="C84" s="13" t="s">
         <v>162</v>
@@ -4571,7 +4592,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="88"/>
+      <c r="A85" s="84"/>
       <c r="B85" s="82"/>
       <c r="C85" s="13" t="s">
         <v>198</v>
@@ -4585,7 +4606,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="88"/>
+      <c r="A86" s="84"/>
       <c r="B86" s="82"/>
       <c r="C86" s="13" t="s">
         <v>168</v>
@@ -4599,7 +4620,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="88"/>
+      <c r="A87" s="84"/>
       <c r="B87" s="82"/>
       <c r="C87" s="13" t="s">
         <v>190</v>
@@ -4613,12 +4634,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="88"/>
-      <c r="B88" s="91"/>
+      <c r="A88" s="84"/>
+      <c r="B88" s="94"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="88"/>
-      <c r="B89" s="90" t="s">
+      <c r="A89" s="84"/>
+      <c r="B89" s="91" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4633,7 +4654,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="88"/>
+      <c r="A90" s="84"/>
       <c r="B90" s="82"/>
       <c r="C90" s="13" t="s">
         <v>109</v>
@@ -4647,7 +4668,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="88"/>
+      <c r="A91" s="84"/>
       <c r="B91" s="82"/>
       <c r="C91" s="13" t="s">
         <v>121</v>
@@ -4661,7 +4682,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="88"/>
+      <c r="A92" s="84"/>
       <c r="B92" s="82"/>
       <c r="C92" s="13" t="s">
         <v>142</v>
@@ -4675,7 +4696,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="88"/>
+      <c r="A93" s="84"/>
       <c r="B93" s="82"/>
       <c r="C93" s="13" t="s">
         <v>156</v>
@@ -4689,7 +4710,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="88"/>
+      <c r="A94" s="84"/>
       <c r="B94" s="82"/>
       <c r="C94" s="13" t="s">
         <v>162</v>
@@ -4703,7 +4724,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="88"/>
+      <c r="A95" s="84"/>
       <c r="B95" s="82"/>
       <c r="C95" s="13" t="s">
         <v>198</v>
@@ -4717,7 +4738,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="88"/>
+      <c r="A96" s="84"/>
       <c r="B96" s="82"/>
       <c r="C96" s="13" t="s">
         <v>168</v>
@@ -4731,7 +4752,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="88"/>
+      <c r="A97" s="84"/>
       <c r="B97" s="82"/>
       <c r="C97" s="13" t="s">
         <v>190</v>
@@ -4745,14 +4766,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="89"/>
-      <c r="B98" s="92"/>
+      <c r="A98" s="90"/>
+      <c r="B98" s="97"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="87" t="s">
+      <c r="A99" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="86" t="s">
+      <c r="B99" s="85" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="26" t="s">
@@ -4767,7 +4788,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="88"/>
+      <c r="A100" s="84"/>
       <c r="B100" s="80"/>
       <c r="C100" s="13" t="s">
         <v>230</v>
@@ -4781,7 +4802,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="88"/>
+      <c r="A101" s="84"/>
       <c r="B101" s="80"/>
       <c r="C101" s="13" t="s">
         <v>151</v>
@@ -4795,7 +4816,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="88"/>
+      <c r="A102" s="84"/>
       <c r="B102" s="81"/>
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
@@ -4803,7 +4824,7 @@
       <c r="F102" s="37"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="88"/>
+      <c r="A103" s="84"/>
       <c r="B103" s="79" t="s">
         <v>330</v>
       </c>
@@ -4819,7 +4840,7 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="88"/>
+      <c r="A104" s="84"/>
       <c r="B104" s="80"/>
       <c r="C104" s="13" t="s">
         <v>335</v>
@@ -4833,7 +4854,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="88"/>
+      <c r="A105" s="84"/>
       <c r="B105" s="80"/>
       <c r="C105" s="13" t="s">
         <v>336</v>
@@ -4847,12 +4868,12 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="88"/>
+      <c r="A106" s="84"/>
       <c r="B106" s="81"/>
       <c r="E106" s="33"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="88"/>
+      <c r="A107" s="84"/>
       <c r="B107" s="79" t="s">
         <v>79</v>
       </c>
@@ -4868,7 +4889,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="88"/>
+      <c r="A108" s="84"/>
       <c r="B108" s="80"/>
       <c r="C108" s="13" t="s">
         <v>152</v>
@@ -4882,7 +4903,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="88"/>
+      <c r="A109" s="84"/>
       <c r="B109" s="81"/>
       <c r="C109" s="37"/>
       <c r="D109" s="37"/>
@@ -4890,8 +4911,8 @@
       <c r="F109" s="37"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="88"/>
-      <c r="B110" s="83" t="s">
+      <c r="A110" s="84"/>
+      <c r="B110" s="86" t="s">
         <v>276</v>
       </c>
       <c r="C110" s="45" t="s">
@@ -4906,8 +4927,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="88"/>
-      <c r="B111" s="84"/>
+      <c r="A111" s="84"/>
+      <c r="B111" s="87"/>
       <c r="C111" s="45" t="s">
         <v>277</v>
       </c>
@@ -4920,18 +4941,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="89"/>
-      <c r="B112" s="85"/>
+      <c r="A112" s="90"/>
+      <c r="B112" s="96"/>
       <c r="C112" s="54"/>
       <c r="D112" s="54"/>
       <c r="E112" s="55"/>
       <c r="F112" s="54"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="87" t="s">
+      <c r="A113" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="B113" s="86" t="s">
+      <c r="B113" s="85" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -4946,7 +4967,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="88"/>
+      <c r="A114" s="99"/>
       <c r="B114" s="80"/>
       <c r="C114" s="13" t="s">
         <v>175</v>
@@ -4959,7 +4980,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="88"/>
+      <c r="A115" s="99"/>
       <c r="B115" s="81"/>
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
@@ -4967,7 +4988,7 @@
       <c r="F115" s="37"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="88"/>
+      <c r="A116" s="99"/>
       <c r="B116" s="79" t="s">
         <v>184</v>
       </c>
@@ -4982,7 +5003,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="88"/>
+      <c r="A117" s="99"/>
       <c r="B117" s="80"/>
       <c r="C117" s="13" t="s">
         <v>182</v>
@@ -4995,7 +5016,7 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="88"/>
+      <c r="A118" s="99"/>
       <c r="B118" s="80"/>
       <c r="C118" s="13" t="s">
         <v>178</v>
@@ -5008,7 +5029,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="88"/>
+      <c r="A119" s="99"/>
       <c r="B119" s="80"/>
       <c r="C119" s="13" t="s">
         <v>180</v>
@@ -5021,7 +5042,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="88"/>
+      <c r="A120" s="99"/>
       <c r="B120" s="80"/>
       <c r="C120" s="13" t="s">
         <v>183</v>
@@ -5034,7 +5055,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="88"/>
+      <c r="A121" s="99"/>
       <c r="B121" s="80"/>
       <c r="C121" s="13" t="s">
         <v>193</v>
@@ -5047,11 +5068,11 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="88"/>
+      <c r="A122" s="99"/>
       <c r="B122" s="80"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="88"/>
+      <c r="A123" s="99"/>
       <c r="B123" s="79" t="s">
         <v>208</v>
       </c>
@@ -5067,7 +5088,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="88"/>
+      <c r="A124" s="99"/>
       <c r="B124" s="80"/>
       <c r="C124" s="13" t="s">
         <v>206</v>
@@ -5080,7 +5101,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="88"/>
+      <c r="A125" s="99"/>
       <c r="B125" s="80"/>
       <c r="C125" s="13" t="s">
         <v>217</v>
@@ -5093,7 +5114,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="88"/>
+      <c r="A126" s="99"/>
       <c r="B126" s="80"/>
       <c r="C126" s="13" t="s">
         <v>207</v>
@@ -5106,7 +5127,7 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="88"/>
+      <c r="A127" s="99"/>
       <c r="B127" s="80"/>
       <c r="C127" s="13" t="s">
         <v>339</v>
@@ -5119,7 +5140,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="88"/>
+      <c r="A128" s="99"/>
       <c r="B128" s="80"/>
       <c r="C128" s="45" t="s">
         <v>363</v>
@@ -5133,7 +5154,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="88"/>
+      <c r="A129" s="99"/>
       <c r="B129" s="80"/>
       <c r="C129" s="45" t="s">
         <v>365</v>
@@ -5147,7 +5168,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="88"/>
+      <c r="A130" s="99"/>
       <c r="B130" s="80"/>
       <c r="C130" s="13" t="s">
         <v>219</v>
@@ -5160,7 +5181,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="88"/>
+      <c r="A131" s="99"/>
       <c r="B131" s="80"/>
       <c r="C131" s="13" t="s">
         <v>223</v>
@@ -5173,7 +5194,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="88"/>
+      <c r="A132" s="99"/>
       <c r="B132" s="80"/>
       <c r="C132" s="13" t="s">
         <v>204</v>
@@ -5186,7 +5207,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="88"/>
+      <c r="A133" s="99"/>
       <c r="B133" s="80"/>
       <c r="C133" s="45" t="s">
         <v>280</v>
@@ -5200,7 +5221,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="88"/>
+      <c r="A134" s="99"/>
       <c r="B134" s="80"/>
       <c r="C134" s="45" t="s">
         <v>283</v>
@@ -5214,7 +5235,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="88"/>
+      <c r="A135" s="99"/>
       <c r="B135" s="80"/>
       <c r="C135" s="45"/>
       <c r="D135" s="45"/>
@@ -5222,7 +5243,7 @@
       <c r="F135" s="45"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="88"/>
+      <c r="A136" s="99"/>
       <c r="B136" s="79" t="s">
         <v>224</v>
       </c>
@@ -5238,8 +5259,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="88"/>
-      <c r="B137" s="80"/>
+      <c r="A137" s="99"/>
+      <c r="B137" s="98"/>
       <c r="C137" s="13" t="s">
         <v>341</v>
       </c>
@@ -5251,8 +5272,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="88"/>
-      <c r="B138" s="80"/>
+      <c r="A138" s="99"/>
+      <c r="B138" s="98"/>
       <c r="C138" s="13" t="s">
         <v>227</v>
       </c>
@@ -5264,8 +5285,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="88"/>
-      <c r="B139" s="80"/>
+      <c r="A139" s="99"/>
+      <c r="B139" s="98"/>
       <c r="C139" s="45" t="s">
         <v>284</v>
       </c>
@@ -5278,8 +5299,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="88"/>
-      <c r="B140" s="80"/>
+      <c r="A140" s="99"/>
+      <c r="B140" s="98"/>
       <c r="C140" s="45" t="s">
         <v>286</v>
       </c>
@@ -5291,8 +5312,59 @@
         <v>215</v>
       </c>
     </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="99"/>
+      <c r="B141" s="81"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="99"/>
+      <c r="B142" s="79" t="s">
+        <v>369</v>
+      </c>
+      <c r="C142" s="35" t="s">
+        <v>370</v>
+      </c>
+      <c r="D142" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="E142" s="35"/>
+      <c r="F142" s="35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="99"/>
+      <c r="B143" s="80"/>
+      <c r="C143" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F143" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="99"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A113:A144"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B116:B122"/>
+    <mergeCell ref="B123:B135"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="A2:A43"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -5302,20 +5374,6 @@
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="B44:B53"/>
     <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B116:B122"/>
-    <mergeCell ref="B136:B140"/>
-    <mergeCell ref="A113:A140"/>
-    <mergeCell ref="B123:B135"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F80A0A4-6952-4D89-A77B-CFF9F2FD1A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B665E4AC-1ADA-4A72-96FD-2ABB47EF7477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="375">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1322,6 +1322,9 @@
   </si>
   <si>
     <t>calc_price</t>
+  </si>
+  <si>
+    <t>kWh_th/a</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1530,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1651,20 +1654,41 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1673,34 +1697,10 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3364,7 +3364,7 @@
         <v>-1E-4</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3460,10 +3460,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="89" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3478,7 +3478,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="84"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="80"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
@@ -3492,7 +3492,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
+      <c r="A4" s="90"/>
       <c r="B4" s="80"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3506,7 +3506,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="84"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="80"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
@@ -3520,7 +3520,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="84"/>
+      <c r="A6" s="90"/>
       <c r="B6" s="80"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
@@ -3534,7 +3534,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="84"/>
+      <c r="A7" s="90"/>
       <c r="B7" s="80"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
@@ -3548,7 +3548,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="84"/>
+      <c r="A8" s="90"/>
       <c r="B8" s="80"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
@@ -3562,7 +3562,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
+      <c r="A9" s="90"/>
       <c r="B9" s="80"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
@@ -3576,7 +3576,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="80"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
@@ -3590,12 +3590,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="80"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="86" t="s">
         <v>232</v>
       </c>
@@ -3611,7 +3611,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
+      <c r="A13" s="90"/>
       <c r="B13" s="87"/>
       <c r="C13" s="45" t="s">
         <v>261</v>
@@ -3625,7 +3625,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
+      <c r="A14" s="90"/>
       <c r="B14" s="87"/>
       <c r="C14" s="45" t="s">
         <v>140</v>
@@ -3639,7 +3639,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="84"/>
+      <c r="A15" s="90"/>
       <c r="B15" s="87"/>
       <c r="C15" s="45" t="s">
         <v>262</v>
@@ -3653,7 +3653,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="84"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="87"/>
       <c r="C16" s="45" t="s">
         <v>84</v>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="84"/>
+      <c r="A17" s="90"/>
       <c r="B17" s="87"/>
       <c r="C17" s="45" t="s">
         <v>142</v>
@@ -3681,7 +3681,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="84"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="87"/>
       <c r="C18" s="45" t="s">
         <v>156</v>
@@ -3695,7 +3695,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="84"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="87"/>
       <c r="C19" s="45" t="s">
         <v>198</v>
@@ -3709,7 +3709,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="84"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="87"/>
       <c r="C20" s="45" t="s">
         <v>168</v>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="84"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="87"/>
       <c r="C21" s="45" t="s">
         <v>190</v>
@@ -3737,15 +3737,15 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
-      <c r="B22" s="88"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="53"/>
       <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="84"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="86" t="s">
         <v>297</v>
       </c>
@@ -3761,7 +3761,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="87"/>
       <c r="C24" s="45" t="s">
         <v>108</v>
@@ -3775,7 +3775,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="87"/>
       <c r="C25" s="45" t="s">
         <v>84</v>
@@ -3789,7 +3789,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="87"/>
       <c r="C26" s="45" t="s">
         <v>320</v>
@@ -3803,7 +3803,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="87"/>
       <c r="C27" s="45" t="s">
         <v>142</v>
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="87"/>
       <c r="C28" s="45" t="s">
         <v>156</v>
@@ -3831,7 +3831,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="84"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="87"/>
       <c r="C29" s="45" t="s">
         <v>198</v>
@@ -3845,7 +3845,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="84"/>
+      <c r="A30" s="90"/>
       <c r="B30" s="87"/>
       <c r="C30" s="45" t="s">
         <v>168</v>
@@ -3859,7 +3859,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="84"/>
+      <c r="A31" s="90"/>
       <c r="B31" s="87"/>
       <c r="C31" s="45" t="s">
         <v>190</v>
@@ -3873,16 +3873,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="84"/>
-      <c r="B32" s="88"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="95"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52"/>
       <c r="E32" s="53"/>
       <c r="F32" s="52"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
-      <c r="B33" s="89" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="96" t="s">
         <v>231</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -3897,8 +3897,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="84"/>
-      <c r="B34" s="89"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="45" t="s">
         <v>108</v>
       </c>
@@ -3911,8 +3911,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="84"/>
-      <c r="B35" s="89"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="45" t="s">
         <v>84</v>
       </c>
@@ -3925,8 +3925,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="84"/>
-      <c r="B36" s="89"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="96"/>
       <c r="C36" s="45" t="s">
         <v>307</v>
       </c>
@@ -3939,8 +3939,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="84"/>
-      <c r="B37" s="89"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="96"/>
       <c r="C37" s="45" t="s">
         <v>274</v>
       </c>
@@ -3953,8 +3953,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="84"/>
-      <c r="B38" s="89"/>
+      <c r="A38" s="90"/>
+      <c r="B38" s="96"/>
       <c r="C38" s="45" t="s">
         <v>142</v>
       </c>
@@ -3967,8 +3967,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="84"/>
-      <c r="B39" s="89"/>
+      <c r="A39" s="90"/>
+      <c r="B39" s="96"/>
       <c r="C39" s="45" t="s">
         <v>156</v>
       </c>
@@ -3981,8 +3981,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="84"/>
-      <c r="B40" s="89"/>
+      <c r="A40" s="90"/>
+      <c r="B40" s="96"/>
       <c r="C40" s="45" t="s">
         <v>198</v>
       </c>
@@ -3995,8 +3995,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="84"/>
-      <c r="B41" s="89"/>
+      <c r="A41" s="90"/>
+      <c r="B41" s="96"/>
       <c r="C41" s="45" t="s">
         <v>168</v>
       </c>
@@ -4009,8 +4009,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="84"/>
-      <c r="B42" s="89"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="96"/>
       <c r="C42" s="45" t="s">
         <v>190</v>
       </c>
@@ -4023,18 +4023,18 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="84"/>
-      <c r="B43" s="89"/>
+      <c r="A43" s="90"/>
+      <c r="B43" s="96"/>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
       <c r="E43" s="50"/>
       <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="83" t="s">
+      <c r="A44" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="93" t="s">
+      <c r="B44" s="98" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="26" t="s">
@@ -4049,7 +4049,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="84"/>
+      <c r="A45" s="90"/>
       <c r="B45" s="82"/>
       <c r="C45" s="13" t="s">
         <v>112</v>
@@ -4063,7 +4063,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="84"/>
+      <c r="A46" s="90"/>
       <c r="B46" s="82"/>
       <c r="C46" s="13" t="s">
         <v>136</v>
@@ -4077,7 +4077,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="84"/>
+      <c r="A47" s="90"/>
       <c r="B47" s="82"/>
       <c r="C47" s="13" t="s">
         <v>137</v>
@@ -4091,7 +4091,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="84"/>
+      <c r="A48" s="90"/>
       <c r="B48" s="82"/>
       <c r="C48" s="13" t="s">
         <v>142</v>
@@ -4105,7 +4105,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="84"/>
+      <c r="A49" s="90"/>
       <c r="B49" s="82"/>
       <c r="C49" s="13" t="s">
         <v>156</v>
@@ -4119,7 +4119,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="84"/>
+      <c r="A50" s="90"/>
       <c r="B50" s="82"/>
       <c r="C50" s="13" t="s">
         <v>198</v>
@@ -4133,7 +4133,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
+      <c r="A51" s="90"/>
       <c r="B51" s="82"/>
       <c r="C51" s="13" t="s">
         <v>168</v>
@@ -4147,7 +4147,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
+      <c r="A52" s="90"/>
       <c r="B52" s="82"/>
       <c r="C52" s="13" t="s">
         <v>190</v>
@@ -4161,152 +4161,149 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
-      <c r="B53" s="94"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="93"/>
       <c r="C53" s="37"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
       <c r="F53" s="37"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
-      <c r="B54" s="89" t="s">
+      <c r="A54" s="90"/>
+      <c r="B54" s="82" t="s">
         <v>344</v>
       </c>
-      <c r="C54" s="45" t="s">
+      <c r="C54" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="45" t="s">
+      <c r="E54" s="31"/>
+      <c r="F54" s="13" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
-      <c r="B55" s="89"/>
-      <c r="C55" s="45" t="s">
+      <c r="A55" s="90"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="45" t="s">
+      <c r="E55" s="33"/>
+      <c r="F55" s="13" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
-      <c r="B56" s="89"/>
-      <c r="C56" s="45" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="66" t="s">
-        <v>133</v>
+      <c r="E56" s="34"/>
+      <c r="F56" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="84"/>
-      <c r="B57" s="89"/>
-      <c r="C57" s="45" t="s">
+      <c r="A57" s="90"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E57" s="50"/>
-      <c r="F57" s="66" t="s">
-        <v>133</v>
+      <c r="E57" s="33"/>
+      <c r="F57" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="84"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="45" t="s">
+      <c r="A58" s="90"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="E58" s="50"/>
-      <c r="F58" s="66" t="s">
+      <c r="E58" s="33"/>
+      <c r="F58" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="84"/>
-      <c r="B59" s="89"/>
-      <c r="C59" s="45" t="s">
+      <c r="A59" s="90"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D59" s="45" t="s">
+      <c r="D59" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="66" t="s">
+      <c r="E59" s="33"/>
+      <c r="F59" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="84"/>
-      <c r="B60" s="89"/>
-      <c r="C60" s="45" t="s">
+      <c r="A60" s="90"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E60" s="50"/>
-      <c r="F60" s="66" t="s">
+      <c r="E60" s="33"/>
+      <c r="F60" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
-      <c r="B61" s="89"/>
-      <c r="C61" s="45" t="s">
+      <c r="A61" s="90"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D61" s="45" t="s">
+      <c r="D61" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E61" s="50"/>
-      <c r="F61" s="66" t="s">
+      <c r="E61" s="33"/>
+      <c r="F61" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="84"/>
-      <c r="B62" s="89"/>
-      <c r="C62" s="45" t="s">
+      <c r="A62" s="90"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E62" s="50"/>
-      <c r="F62" s="66" t="s">
+      <c r="E62" s="33"/>
+      <c r="F62" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="84"/>
-      <c r="B63" s="95"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="45"/>
+      <c r="A63" s="90"/>
+      <c r="B63" s="93"/>
+      <c r="E63" s="33"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="84"/>
-      <c r="B64" s="91" t="s">
+      <c r="A64" s="90"/>
+      <c r="B64" s="92" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="35" t="s">
@@ -4321,7 +4318,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="82"/>
       <c r="C65" s="13" t="s">
         <v>114</v>
@@ -4335,7 +4332,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="84"/>
+      <c r="A66" s="90"/>
       <c r="B66" s="80"/>
       <c r="C66" s="13" t="s">
         <v>112</v>
@@ -4349,7 +4346,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
+      <c r="A67" s="90"/>
       <c r="B67" s="80"/>
       <c r="C67" s="13" t="s">
         <v>108</v>
@@ -4363,7 +4360,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
+      <c r="A68" s="90"/>
       <c r="B68" s="80"/>
       <c r="C68" s="13" t="s">
         <v>127</v>
@@ -4377,7 +4374,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="84"/>
+      <c r="A69" s="90"/>
       <c r="B69" s="80"/>
       <c r="C69" s="13" t="s">
         <v>128</v>
@@ -4391,7 +4388,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="84"/>
+      <c r="A70" s="90"/>
       <c r="B70" s="80"/>
       <c r="C70" s="13" t="s">
         <v>142</v>
@@ -4405,7 +4402,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="84"/>
+      <c r="A71" s="90"/>
       <c r="B71" s="80"/>
       <c r="C71" s="13" t="s">
         <v>156</v>
@@ -4419,7 +4416,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="84"/>
+      <c r="A72" s="90"/>
       <c r="B72" s="80"/>
       <c r="C72" s="13" t="s">
         <v>198</v>
@@ -4433,7 +4430,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="80"/>
       <c r="C73" s="13" t="s">
         <v>168</v>
@@ -4447,7 +4444,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="84"/>
+      <c r="A74" s="90"/>
       <c r="B74" s="80"/>
       <c r="C74" s="13" t="s">
         <v>190</v>
@@ -4461,18 +4458,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="90"/>
-      <c r="B75" s="92"/>
+      <c r="A75" s="91"/>
+      <c r="B75" s="97"/>
       <c r="C75" s="41"/>
       <c r="D75" s="41"/>
       <c r="E75" s="42"/>
       <c r="F75" s="41"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="83" t="s">
+      <c r="A76" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="85" t="s">
+      <c r="B76" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="26" t="s">
@@ -4487,7 +4484,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="84"/>
+      <c r="A77" s="90"/>
       <c r="B77" s="80"/>
       <c r="C77" s="13" t="s">
         <v>154</v>
@@ -4501,13 +4498,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="84"/>
+      <c r="A78" s="90"/>
       <c r="B78" s="81"/>
       <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="84"/>
-      <c r="B79" s="91" t="s">
+      <c r="A79" s="90"/>
+      <c r="B79" s="92" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="35" t="s">
@@ -4522,7 +4519,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="84"/>
+      <c r="A80" s="90"/>
       <c r="B80" s="82"/>
       <c r="C80" s="13" t="s">
         <v>108</v>
@@ -4536,7 +4533,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="84"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="82"/>
       <c r="C81" s="13" t="s">
         <v>123</v>
@@ -4550,7 +4547,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="84"/>
+      <c r="A82" s="90"/>
       <c r="B82" s="82"/>
       <c r="C82" s="13" t="s">
         <v>142</v>
@@ -4564,7 +4561,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="84"/>
+      <c r="A83" s="90"/>
       <c r="B83" s="82"/>
       <c r="C83" s="13" t="s">
         <v>156</v>
@@ -4578,7 +4575,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="84"/>
+      <c r="A84" s="90"/>
       <c r="B84" s="82"/>
       <c r="C84" s="13" t="s">
         <v>162</v>
@@ -4592,7 +4589,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="84"/>
+      <c r="A85" s="90"/>
       <c r="B85" s="82"/>
       <c r="C85" s="13" t="s">
         <v>198</v>
@@ -4606,7 +4603,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="84"/>
+      <c r="A86" s="90"/>
       <c r="B86" s="82"/>
       <c r="C86" s="13" t="s">
         <v>168</v>
@@ -4620,7 +4617,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="84"/>
+      <c r="A87" s="90"/>
       <c r="B87" s="82"/>
       <c r="C87" s="13" t="s">
         <v>190</v>
@@ -4634,12 +4631,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="84"/>
-      <c r="B88" s="94"/>
+      <c r="A88" s="90"/>
+      <c r="B88" s="93"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="84"/>
-      <c r="B89" s="91" t="s">
+      <c r="A89" s="90"/>
+      <c r="B89" s="92" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4654,7 +4651,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="84"/>
+      <c r="A90" s="90"/>
       <c r="B90" s="82"/>
       <c r="C90" s="13" t="s">
         <v>109</v>
@@ -4668,7 +4665,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="84"/>
+      <c r="A91" s="90"/>
       <c r="B91" s="82"/>
       <c r="C91" s="13" t="s">
         <v>121</v>
@@ -4682,7 +4679,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="84"/>
+      <c r="A92" s="90"/>
       <c r="B92" s="82"/>
       <c r="C92" s="13" t="s">
         <v>142</v>
@@ -4696,7 +4693,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="84"/>
+      <c r="A93" s="90"/>
       <c r="B93" s="82"/>
       <c r="C93" s="13" t="s">
         <v>156</v>
@@ -4710,7 +4707,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="84"/>
+      <c r="A94" s="90"/>
       <c r="B94" s="82"/>
       <c r="C94" s="13" t="s">
         <v>162</v>
@@ -4724,7 +4721,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="84"/>
+      <c r="A95" s="90"/>
       <c r="B95" s="82"/>
       <c r="C95" s="13" t="s">
         <v>198</v>
@@ -4738,7 +4735,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="84"/>
+      <c r="A96" s="90"/>
       <c r="B96" s="82"/>
       <c r="C96" s="13" t="s">
         <v>168</v>
@@ -4752,7 +4749,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="84"/>
+      <c r="A97" s="90"/>
       <c r="B97" s="82"/>
       <c r="C97" s="13" t="s">
         <v>190</v>
@@ -4766,14 +4763,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="90"/>
-      <c r="B98" s="97"/>
+      <c r="A98" s="91"/>
+      <c r="B98" s="94"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="83" t="s">
+      <c r="A99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="85" t="s">
+      <c r="B99" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="26" t="s">
@@ -4788,7 +4785,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="84"/>
+      <c r="A100" s="90"/>
       <c r="B100" s="80"/>
       <c r="C100" s="13" t="s">
         <v>230</v>
@@ -4802,7 +4799,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="84"/>
+      <c r="A101" s="90"/>
       <c r="B101" s="80"/>
       <c r="C101" s="13" t="s">
         <v>151</v>
@@ -4816,7 +4813,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="84"/>
+      <c r="A102" s="90"/>
       <c r="B102" s="81"/>
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
@@ -4824,7 +4821,7 @@
       <c r="F102" s="37"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="84"/>
+      <c r="A103" s="90"/>
       <c r="B103" s="79" t="s">
         <v>330</v>
       </c>
@@ -4840,7 +4837,7 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="84"/>
+      <c r="A104" s="90"/>
       <c r="B104" s="80"/>
       <c r="C104" s="13" t="s">
         <v>335</v>
@@ -4854,7 +4851,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="84"/>
+      <c r="A105" s="90"/>
       <c r="B105" s="80"/>
       <c r="C105" s="13" t="s">
         <v>336</v>
@@ -4868,12 +4865,12 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="84"/>
+      <c r="A106" s="90"/>
       <c r="B106" s="81"/>
       <c r="E106" s="33"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="84"/>
+      <c r="A107" s="90"/>
       <c r="B107" s="79" t="s">
         <v>79</v>
       </c>
@@ -4889,7 +4886,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="84"/>
+      <c r="A108" s="90"/>
       <c r="B108" s="80"/>
       <c r="C108" s="13" t="s">
         <v>152</v>
@@ -4903,7 +4900,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="84"/>
+      <c r="A109" s="90"/>
       <c r="B109" s="81"/>
       <c r="C109" s="37"/>
       <c r="D109" s="37"/>
@@ -4911,7 +4908,7 @@
       <c r="F109" s="37"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="84"/>
+      <c r="A110" s="90"/>
       <c r="B110" s="86" t="s">
         <v>276</v>
       </c>
@@ -4927,7 +4924,7 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="84"/>
+      <c r="A111" s="90"/>
       <c r="B111" s="87"/>
       <c r="C111" s="45" t="s">
         <v>277</v>
@@ -4941,18 +4938,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="90"/>
-      <c r="B112" s="96"/>
+      <c r="A112" s="91"/>
+      <c r="B112" s="88"/>
       <c r="C112" s="54"/>
       <c r="D112" s="54"/>
       <c r="E112" s="55"/>
       <c r="F112" s="54"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="83" t="s">
+      <c r="A113" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="B113" s="85" t="s">
+      <c r="B113" s="89" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -4967,7 +4964,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="99"/>
+      <c r="A114" s="85"/>
       <c r="B114" s="80"/>
       <c r="C114" s="13" t="s">
         <v>175</v>
@@ -4980,7 +4977,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="99"/>
+      <c r="A115" s="85"/>
       <c r="B115" s="81"/>
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
@@ -4988,7 +4985,7 @@
       <c r="F115" s="37"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="99"/>
+      <c r="A116" s="85"/>
       <c r="B116" s="79" t="s">
         <v>184</v>
       </c>
@@ -5003,7 +5000,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="99"/>
+      <c r="A117" s="85"/>
       <c r="B117" s="80"/>
       <c r="C117" s="13" t="s">
         <v>182</v>
@@ -5016,7 +5013,7 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="99"/>
+      <c r="A118" s="85"/>
       <c r="B118" s="80"/>
       <c r="C118" s="13" t="s">
         <v>178</v>
@@ -5029,7 +5026,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="99"/>
+      <c r="A119" s="85"/>
       <c r="B119" s="80"/>
       <c r="C119" s="13" t="s">
         <v>180</v>
@@ -5042,7 +5039,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="99"/>
+      <c r="A120" s="85"/>
       <c r="B120" s="80"/>
       <c r="C120" s="13" t="s">
         <v>183</v>
@@ -5055,7 +5052,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="99"/>
+      <c r="A121" s="85"/>
       <c r="B121" s="80"/>
       <c r="C121" s="13" t="s">
         <v>193</v>
@@ -5068,11 +5065,11 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="99"/>
+      <c r="A122" s="85"/>
       <c r="B122" s="80"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="99"/>
+      <c r="A123" s="85"/>
       <c r="B123" s="79" t="s">
         <v>208</v>
       </c>
@@ -5088,7 +5085,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="99"/>
+      <c r="A124" s="85"/>
       <c r="B124" s="80"/>
       <c r="C124" s="13" t="s">
         <v>206</v>
@@ -5101,7 +5098,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="99"/>
+      <c r="A125" s="85"/>
       <c r="B125" s="80"/>
       <c r="C125" s="13" t="s">
         <v>217</v>
@@ -5114,7 +5111,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="99"/>
+      <c r="A126" s="85"/>
       <c r="B126" s="80"/>
       <c r="C126" s="13" t="s">
         <v>207</v>
@@ -5127,7 +5124,7 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="99"/>
+      <c r="A127" s="85"/>
       <c r="B127" s="80"/>
       <c r="C127" s="13" t="s">
         <v>339</v>
@@ -5140,7 +5137,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="99"/>
+      <c r="A128" s="85"/>
       <c r="B128" s="80"/>
       <c r="C128" s="45" t="s">
         <v>363</v>
@@ -5154,7 +5151,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="99"/>
+      <c r="A129" s="85"/>
       <c r="B129" s="80"/>
       <c r="C129" s="45" t="s">
         <v>365</v>
@@ -5168,7 +5165,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="99"/>
+      <c r="A130" s="85"/>
       <c r="B130" s="80"/>
       <c r="C130" s="13" t="s">
         <v>219</v>
@@ -5181,7 +5178,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="99"/>
+      <c r="A131" s="85"/>
       <c r="B131" s="80"/>
       <c r="C131" s="13" t="s">
         <v>223</v>
@@ -5194,7 +5191,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="99"/>
+      <c r="A132" s="85"/>
       <c r="B132" s="80"/>
       <c r="C132" s="13" t="s">
         <v>204</v>
@@ -5207,7 +5204,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="99"/>
+      <c r="A133" s="85"/>
       <c r="B133" s="80"/>
       <c r="C133" s="45" t="s">
         <v>280</v>
@@ -5221,7 +5218,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="99"/>
+      <c r="A134" s="85"/>
       <c r="B134" s="80"/>
       <c r="C134" s="45" t="s">
         <v>283</v>
@@ -5235,7 +5232,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="99"/>
+      <c r="A135" s="85"/>
       <c r="B135" s="80"/>
       <c r="C135" s="45"/>
       <c r="D135" s="45"/>
@@ -5243,7 +5240,7 @@
       <c r="F135" s="45"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="99"/>
+      <c r="A136" s="85"/>
       <c r="B136" s="79" t="s">
         <v>224</v>
       </c>
@@ -5259,8 +5256,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="99"/>
-      <c r="B137" s="98"/>
+      <c r="A137" s="85"/>
+      <c r="B137" s="83"/>
       <c r="C137" s="13" t="s">
         <v>341</v>
       </c>
@@ -5272,8 +5269,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="99"/>
-      <c r="B138" s="98"/>
+      <c r="A138" s="85"/>
+      <c r="B138" s="83"/>
       <c r="C138" s="13" t="s">
         <v>227</v>
       </c>
@@ -5285,8 +5282,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="99"/>
-      <c r="B139" s="98"/>
+      <c r="A139" s="85"/>
+      <c r="B139" s="83"/>
       <c r="C139" s="45" t="s">
         <v>284</v>
       </c>
@@ -5299,8 +5296,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="99"/>
-      <c r="B140" s="98"/>
+      <c r="A140" s="85"/>
+      <c r="B140" s="83"/>
       <c r="C140" s="45" t="s">
         <v>286</v>
       </c>
@@ -5313,11 +5310,11 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="99"/>
+      <c r="A141" s="85"/>
       <c r="B141" s="81"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="99"/>
+      <c r="A142" s="85"/>
       <c r="B142" s="79" t="s">
         <v>369</v>
       </c>
@@ -5333,7 +5330,7 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="99"/>
+      <c r="A143" s="85"/>
       <c r="B143" s="80"/>
       <c r="C143" s="13" t="s">
         <v>372</v>
@@ -5346,10 +5343,19 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="99"/>
+      <c r="A144" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="B136:B141"/>
     <mergeCell ref="A113:A144"/>
@@ -5365,15 +5371,6 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791564D0-582B-4E87-BB58-024D24D106E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8650307B-591C-4BF2-AAAF-55EFC5B7390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -480,9 +480,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -765,9 +762,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1297,6 +1291,12 @@
   </si>
   <si>
     <t>kWh_th/a</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1449,67 +1449,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1522,6 +1477,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1857,10 +1857,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="22" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
@@ -1889,54 +1889,54 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="37"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="9">
         <v>50</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="10">
         <v>1000</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1944,15 +1944,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>0.03</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -1960,15 +1960,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>20</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -1976,15 +1976,15 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>0.08</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -1992,33 +1992,33 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="33" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="36">
+      <c r="E8" s="21">
         <v>1.5</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>233</v>
+      <c r="F8" s="16" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" s="13">
+        <v>233</v>
+      </c>
+      <c r="E9" s="9">
         <v>285.39999999999998</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -2026,31 +2026,31 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="13">
+        <v>234</v>
+      </c>
+      <c r="E10" s="9">
         <v>5110</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>241</v>
+      <c r="F10" s="9" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" s="15">
+        <v>235</v>
+      </c>
+      <c r="E11" s="11">
         <v>0.05</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -2058,47 +2058,47 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="13">
+        <v>236</v>
+      </c>
+      <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.375</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="13">
-        <v>1.375</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="16">
+        <v>237</v>
+      </c>
+      <c r="E14" s="12">
         <v>25</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -2106,81 +2106,81 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="21" t="s">
+      <c r="A15" s="32"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="22">
+      <c r="D15" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="15">
         <v>0.08</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="E16" s="25">
+      <c r="D16" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="E16" s="17">
         <v>3.7</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E17" s="15">
+        <v>290</v>
+      </c>
+      <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E18" s="15">
+        <v>291</v>
+      </c>
+      <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E19" s="15">
+        <v>292</v>
+      </c>
+      <c r="E19" s="11">
         <v>0.02</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -2188,15 +2188,15 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E20" s="15">
+        <v>293</v>
+      </c>
+      <c r="E20" s="11">
         <v>20</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -2204,81 +2204,81 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="21" t="s">
+      <c r="A21" s="32"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="E21" s="22">
+      <c r="D21" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="15">
         <v>0.05</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="19" t="s">
-        <v>231</v>
+      <c r="A22" s="32"/>
+      <c r="B22" s="35" t="s">
+        <v>229</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E22" s="13">
+        <v>243</v>
+      </c>
+      <c r="E22" s="9">
         <v>0.5</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1.75</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="E23" s="13">
-        <v>1.75</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="19"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" s="13">
+        <v>244</v>
+      </c>
+      <c r="E24" s="9">
         <v>7000</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="19"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="E25" s="15">
+        <v>245</v>
+      </c>
+      <c r="E25" s="11">
         <v>0.05</v>
       </c>
       <c r="F25" s="6" t="s">
@@ -2286,15 +2286,15 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="19"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" s="16">
+        <v>246</v>
+      </c>
+      <c r="E26" s="12">
         <v>15</v>
       </c>
       <c r="F26" s="6" t="s">
@@ -2302,15 +2302,15 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" s="15">
+        <v>247</v>
+      </c>
+      <c r="E27" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F27" s="6" t="s">
@@ -2318,35 +2318,35 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="13">
         <v>490</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>93</v>
+      <c r="F28" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>0.01</v>
       </c>
       <c r="F29" s="6" t="s">
@@ -2354,15 +2354,15 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="12">
         <v>20</v>
       </c>
       <c r="F30" s="6" t="s">
@@ -2370,31 +2370,31 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="23">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="11">
         <v>0.83299999999999996</v>
       </c>
       <c r="F32" s="6" t="s">
@@ -2402,15 +2402,15 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="19"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="11">
         <v>0.83299999999999996</v>
       </c>
       <c r="F33" s="6" t="s">
@@ -2418,15 +2418,15 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="11">
         <v>0.05</v>
       </c>
       <c r="F34" s="6" t="s">
@@ -2434,49 +2434,49 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="21" t="s">
+      <c r="A35" s="32"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="15">
         <v>0</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>95</v>
+      <c r="F35" s="14" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="A36" s="32"/>
+      <c r="B36" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="E36" s="18">
+      <c r="D36" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E36" s="13">
         <v>2.83</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>344</v>
+      <c r="F36" s="7" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="19"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E37" s="15">
+        <v>335</v>
+      </c>
+      <c r="E37" s="11">
         <v>0.03</v>
       </c>
       <c r="F37" s="6" t="s">
@@ -2484,15 +2484,15 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="19"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="16">
+        <v>336</v>
+      </c>
+      <c r="E38" s="12">
         <v>30</v>
       </c>
       <c r="F38" s="6" t="s">
@@ -2500,31 +2500,31 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="19"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E39" s="15">
+        <v>337</v>
+      </c>
+      <c r="E39" s="11">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="19"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E40" s="15">
+        <v>338</v>
+      </c>
+      <c r="E40" s="11">
         <v>0.98</v>
       </c>
       <c r="F40" s="6" t="s">
@@ -2532,15 +2532,15 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="19"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E41" s="15">
+        <v>339</v>
+      </c>
+      <c r="E41" s="11">
         <v>0.98</v>
       </c>
       <c r="F41" s="6" t="s">
@@ -2548,15 +2548,15 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="19"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="E42" s="15">
+        <v>340</v>
+      </c>
+      <c r="E42" s="11">
         <v>0.05</v>
       </c>
       <c r="F42" s="6" t="s">
@@ -2564,49 +2564,49 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="21" t="s">
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="E43" s="22">
+      <c r="D43" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="E43" s="15">
         <v>0</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="32"/>
+      <c r="B44" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="17">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F44" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="25">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="9">
         <f>E46*4</f>
         <v>424</v>
       </c>
@@ -2615,15 +2615,15 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="9">
         <v>106</v>
       </c>
       <c r="F46" s="6" t="s">
@@ -2631,15 +2631,15 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F47" s="6" t="s">
@@ -2647,15 +2647,15 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="11">
         <v>0.93500000000000005</v>
       </c>
       <c r="F48" s="6" t="s">
@@ -2663,15 +2663,15 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="11">
         <v>0.93500000000000005</v>
       </c>
       <c r="F49" s="6" t="s">
@@ -2679,15 +2679,15 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="9">
         <v>0.25</v>
       </c>
       <c r="F50" s="6" t="s">
@@ -2695,31 +2695,31 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="6" t="s">
         <v>88</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="11">
         <v>0</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="12">
         <v>15</v>
       </c>
       <c r="F52" s="6" t="s">
@@ -2727,62 +2727,62 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="26"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="28" t="s">
+      <c r="A53" s="33"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="D53" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="19">
         <v>0.1</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="8">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="23" t="s">
+      <c r="A55" s="32"/>
+      <c r="B55" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="17">
         <v>0.99</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F55" s="16" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="19"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="6" t="s">
         <v>10</v>
       </c>
@@ -2797,8 +2797,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="19"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="6" t="s">
         <v>17</v>
       </c>
@@ -2813,15 +2813,15 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="19"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="9">
         <v>0</v>
       </c>
       <c r="F58" s="6" t="s">
@@ -2829,15 +2829,15 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="19"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="12">
         <v>25</v>
       </c>
       <c r="F59" s="6" t="s">
@@ -2845,15 +2845,15 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="19"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="9">
         <v>1000000</v>
       </c>
       <c r="F60" s="6" t="s">
@@ -2861,42 +2861,42 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="21" t="s">
+      <c r="A61" s="32"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="23" t="s">
+      <c r="A62" s="32"/>
+      <c r="B62" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="17">
         <v>0.997</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="19"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="6" t="s">
         <v>10</v>
       </c>
@@ -2911,8 +2911,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="19"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="6" t="s">
         <v>17</v>
       </c>
@@ -2927,8 +2927,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="19"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="6" t="s">
         <v>18</v>
       </c>
@@ -2943,15 +2943,15 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="19"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="12">
         <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
@@ -2959,15 +2959,15 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="19"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="20">
         <v>1000000</v>
       </c>
       <c r="F67" s="6" t="s">
@@ -2975,93 +2975,93 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="26"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="28" t="s">
+      <c r="A68" s="33"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="29">
+      <c r="E68" s="19">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="40" t="s">
+      <c r="B69" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="41" t="s">
+      <c r="C69" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="41" t="s">
+      <c r="D69" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="42">
+      <c r="E69" s="27">
         <v>-1E-4</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="37" t="s">
+      <c r="A70" s="32"/>
+      <c r="B70" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="E70" s="15">
+      <c r="E70" s="11">
         <v>-1E-4</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="43" t="s">
+      <c r="A71" s="32"/>
+      <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="44" t="s">
+      <c r="C71" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="45">
+      <c r="E71" s="30">
         <v>-1.5</v>
       </c>
-      <c r="F71" s="44" t="s">
+      <c r="F71" s="29" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="26"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="D72" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C72" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="E72" s="29">
+      <c r="D72" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E72" s="19">
         <v>-0.6</v>
       </c>
-      <c r="F72" s="28" t="s">
-        <v>290</v>
+      <c r="F72" s="18" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -3121,1069 +3121,1069 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="13"/>
+        <v>115</v>
+      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="E4" s="10"/>
       <c r="F4" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="32"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="32"/>
+      <c r="B12" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="21"/>
+      <c r="F12" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="6" t="s">
+      <c r="D14" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="32"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="11"/>
+      <c r="F15" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="6" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="E19" s="12"/>
+      <c r="F19" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="32"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="21"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="33" t="s">
-        <v>288</v>
+      <c r="A23" s="32"/>
+      <c r="B23" s="42" t="s">
+        <v>286</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="13"/>
+        <v>299</v>
+      </c>
+      <c r="E23" s="9"/>
       <c r="F23" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="13"/>
+        <v>300</v>
+      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="32"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="32"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="32"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="32"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="32"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="E30" s="11"/>
+      <c r="F30" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="32"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E31" s="15"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="21"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="19" t="s">
-        <v>231</v>
+      <c r="A33" s="32"/>
+      <c r="B33" s="35" t="s">
+        <v>229</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E33" s="13"/>
+        <v>264</v>
+      </c>
+      <c r="E33" s="9"/>
       <c r="F33" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E34" s="13"/>
+        <v>265</v>
+      </c>
+      <c r="E34" s="9"/>
       <c r="F34" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="19"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="32"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="11"/>
+      <c r="F36" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="6" t="s">
+      <c r="E39" s="12"/>
+      <c r="F39" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="6" t="s">
+      <c r="E40" s="12"/>
+      <c r="F40" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41" s="11"/>
+      <c r="F41" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" s="11"/>
+      <c r="F42" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="32"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="11"/>
+      <c r="F45" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="32"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="12"/>
+      <c r="F46" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="32"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" s="11"/>
+      <c r="F47" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="32"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="6" t="s">
+      <c r="D48" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="11"/>
+      <c r="F48" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="32"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="F49" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="32"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" s="11"/>
+      <c r="F50" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="32"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="11"/>
+      <c r="F51" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="32"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E52" s="11"/>
+      <c r="F52" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="32"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="14"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="32"/>
+      <c r="B54" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="32"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E56" s="12"/>
+      <c r="F56" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E57" s="11"/>
+      <c r="F57" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11"/>
-      <c r="B43" s="19"/>
-      <c r="E43" s="15"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="D58" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E59" s="11"/>
+      <c r="F59" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E60" s="11"/>
+      <c r="F60" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="32"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E61" s="11"/>
+      <c r="F61" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="32"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E62" s="11"/>
+      <c r="F62" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="32"/>
+      <c r="B63" s="36"/>
+      <c r="E63" s="11"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="32"/>
+      <c r="B64" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E64" s="17"/>
+      <c r="F64" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65" s="11"/>
+      <c r="F65" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="32"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E66" s="9"/>
+      <c r="F66" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="16"/>
-      <c r="F46" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="21"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="20"/>
-      <c r="E63" s="15"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E64" s="25"/>
-      <c r="F64" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="6" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="13"/>
+        <v>185</v>
+      </c>
+      <c r="E67" s="9"/>
       <c r="F67" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="32"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D69" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" s="15"/>
+      <c r="E69" s="11"/>
       <c r="F69" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E70" s="13"/>
+        <v>145</v>
+      </c>
+      <c r="E70" s="9"/>
       <c r="F70" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E71" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="E71" s="11"/>
       <c r="F71" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="E72" s="11"/>
       <c r="F72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="E73" s="11"/>
       <c r="F73" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E74" s="15"/>
+        <v>192</v>
+      </c>
+      <c r="E74" s="11"/>
       <c r="F74" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="26"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="28"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="18"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E76" s="18"/>
-      <c r="F76" s="9" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
+      <c r="A77" s="32"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="E77" s="9"/>
       <c r="F77" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="30"/>
-      <c r="E78" s="13"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="43"/>
+      <c r="E78" s="9"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="23" t="s">
+      <c r="A79" s="32"/>
+      <c r="B79" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D79" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E79" s="25"/>
-      <c r="F79" s="24" t="s">
+      <c r="C79" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="16" t="s">
         <v>99</v>
       </c>
+      <c r="E79" s="17"/>
+      <c r="F79" s="16" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="19"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="6" t="s">
@@ -4191,131 +4191,131 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="19"/>
+      <c r="A81" s="32"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="19"/>
+      <c r="A82" s="32"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E82" s="13"/>
+        <v>144</v>
+      </c>
+      <c r="E82" s="9"/>
       <c r="F82" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="11"/>
-      <c r="B83" s="19"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E83" s="16"/>
+      <c r="E83" s="12"/>
       <c r="F83" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="11"/>
-      <c r="B84" s="19"/>
+      <c r="A84" s="32"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E84" s="13"/>
+      <c r="E84" s="9"/>
       <c r="F84" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="11"/>
-      <c r="B85" s="19"/>
+      <c r="A85" s="32"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E85" s="13"/>
+      <c r="E85" s="9"/>
       <c r="F85" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="11"/>
-      <c r="B86" s="19"/>
+      <c r="A86" s="32"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E86" s="15"/>
+        <v>169</v>
+      </c>
+      <c r="E86" s="11"/>
       <c r="F86" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="11"/>
-      <c r="B87" s="19"/>
+      <c r="A87" s="32"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D87" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E87" s="15"/>
+      <c r="E87" s="11"/>
       <c r="F87" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="20"/>
+      <c r="A88" s="32"/>
+      <c r="B88" s="36"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="11"/>
-      <c r="B89" s="23" t="s">
+      <c r="A89" s="32"/>
+      <c r="B89" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24" t="s">
-        <v>99</v>
+      <c r="C89" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E89" s="17"/>
+      <c r="F89" s="16" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="11"/>
-      <c r="B90" s="19"/>
+      <c r="A90" s="32"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="6" t="s">
@@ -4323,678 +4323,687 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="11"/>
-      <c r="B91" s="19"/>
+      <c r="A91" s="32"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="11"/>
-      <c r="B92" s="19"/>
+      <c r="A92" s="32"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="11"/>
-      <c r="B93" s="19"/>
+      <c r="A93" s="32"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E93" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="E93" s="12"/>
       <c r="F93" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="32"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E94" s="20"/>
+      <c r="F94" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="32"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" s="20"/>
+      <c r="F95" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="32"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="11"/>
+      <c r="F96" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="32"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" s="11"/>
+      <c r="F97" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="33"/>
+      <c r="B98" s="38"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E99" s="8"/>
+      <c r="F99" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="32"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E100" s="11"/>
+      <c r="F100" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="32"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="11"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E94" s="31"/>
-      <c r="F94" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="11"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E95" s="31"/>
-      <c r="F95" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="11"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E96" s="15"/>
-      <c r="F96" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="11"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D97" s="6" t="s">
+      <c r="D101" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E101" s="11"/>
+      <c r="F101" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="32"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="14"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="32"/>
+      <c r="B103" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E103" s="11"/>
+      <c r="F103" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="32"/>
+      <c r="B104" s="39"/>
+      <c r="C104" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E104" s="11"/>
+      <c r="F104" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="32"/>
+      <c r="B105" s="39"/>
+      <c r="C105" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E105" s="11"/>
+      <c r="F105" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="32"/>
+      <c r="B106" s="43"/>
+      <c r="E106" s="11"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="32"/>
+      <c r="B107" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E107" s="17"/>
+      <c r="F107" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="32"/>
+      <c r="B108" s="39"/>
+      <c r="C108" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E108" s="11"/>
+      <c r="F108" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="32"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="14"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="32"/>
+      <c r="B110" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E110" s="11"/>
+      <c r="F110" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="32"/>
+      <c r="B111" s="39"/>
+      <c r="C111" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E111" s="11"/>
+      <c r="F111" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="33"/>
+      <c r="B112" s="40"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="18"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="45"/>
+      <c r="B114" s="39"/>
+      <c r="C114" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="45"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="45"/>
+      <c r="B116" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="45"/>
+      <c r="B117" s="39"/>
+      <c r="C117" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="45"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="45"/>
+      <c r="B119" s="39"/>
+      <c r="C119" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="45"/>
+      <c r="B120" s="39"/>
+      <c r="C120" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="45"/>
+      <c r="B121" s="39"/>
+      <c r="C121" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E97" s="15"/>
-      <c r="F97" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="26"/>
-      <c r="B98" s="32"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E99" s="10"/>
-      <c r="F99" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="11"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="E100" s="15"/>
-      <c r="F100" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="11"/>
-      <c r="B101" s="12"/>
-      <c r="C101" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="11"/>
-      <c r="B102" s="30"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="21"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="11"/>
-      <c r="B103" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="11"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="6" t="s">
+      <c r="D121" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="45"/>
+      <c r="B122" s="39"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="45"/>
+      <c r="B123" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" s="16"/>
+      <c r="F123" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="45"/>
+      <c r="B124" s="39"/>
+      <c r="C124" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="45"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="45"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="45"/>
+      <c r="B127" s="39"/>
+      <c r="C127" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="45"/>
+      <c r="B128" s="39"/>
+      <c r="C128" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="45"/>
+      <c r="B129" s="39"/>
+      <c r="C129" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="45"/>
+      <c r="B130" s="39"/>
+      <c r="C130" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="45"/>
+      <c r="B131" s="39"/>
+      <c r="C131" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="45"/>
+      <c r="B132" s="39"/>
+      <c r="C132" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="45"/>
+      <c r="B133" s="39"/>
+      <c r="C133" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="45"/>
+      <c r="B134" s="39"/>
+      <c r="C134" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="45"/>
+      <c r="B135" s="39"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="45"/>
+      <c r="B136" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="E136" s="16"/>
+      <c r="F136" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="45"/>
+      <c r="B137" s="44"/>
+      <c r="C137" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="45"/>
+      <c r="B138" s="44"/>
+      <c r="C138" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="45"/>
+      <c r="B139" s="44"/>
+      <c r="C139" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="45"/>
+      <c r="B140" s="44"/>
+      <c r="C140" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D140" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D104" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E104" s="15"/>
-      <c r="F104" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="11"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="11"/>
-      <c r="B106" s="30"/>
-      <c r="E106" s="15"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="11"/>
-      <c r="B107" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C107" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="D107" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E107" s="25"/>
-      <c r="F107" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="11"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="11"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="21"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="22"/>
-      <c r="F109" s="21"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="11"/>
-      <c r="B110" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="11"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="26"/>
-      <c r="B112" s="27"/>
-      <c r="C112" s="28"/>
-      <c r="D112" s="28"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="28"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="34"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="34"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="34"/>
-      <c r="B116" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="34"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="34"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="34"/>
-      <c r="B119" s="12"/>
-      <c r="C119" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="34"/>
-      <c r="B120" s="12"/>
-      <c r="C120" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="34"/>
-      <c r="B121" s="12"/>
-      <c r="C121" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="34"/>
-      <c r="B122" s="12"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="34"/>
-      <c r="B123" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="C123" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D123" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="24"/>
-      <c r="F123" s="24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="34"/>
-      <c r="B124" s="12"/>
-      <c r="C124" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="34"/>
-      <c r="B125" s="12"/>
-      <c r="C125" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="34"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="34"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="34"/>
-      <c r="B128" s="12"/>
-      <c r="C128" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="34"/>
-      <c r="B129" s="12"/>
-      <c r="C129" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="34"/>
-      <c r="B130" s="12"/>
-      <c r="C130" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="34"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D131" s="6" t="s">
+      <c r="F140" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F131" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="34"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="34"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="34"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="34"/>
-      <c r="B135" s="12"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="34"/>
-      <c r="B136" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="C136" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="D136" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E136" s="24"/>
-      <c r="F136" s="24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="34"/>
-      <c r="B137" s="35"/>
-      <c r="C137" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="34"/>
-      <c r="B138" s="35"/>
-      <c r="C138" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="34"/>
-      <c r="B139" s="35"/>
-      <c r="C139" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="34"/>
-      <c r="B140" s="35"/>
-      <c r="C140" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="34"/>
-      <c r="B141" s="30"/>
+      <c r="A141" s="45"/>
+      <c r="B141" s="43"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="34"/>
-      <c r="B142" s="33" t="s">
+      <c r="A142" s="45"/>
+      <c r="B142" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="D142" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="C142" s="24" t="s">
+      <c r="E142" s="16"/>
+      <c r="F142" s="16" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="45"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="D142" s="24" t="s">
+      <c r="D143" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="E142" s="24"/>
-      <c r="F142" s="24" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="34"/>
-      <c r="B143" s="12"/>
-      <c r="C143" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>364</v>
-      </c>
       <c r="F143" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="34"/>
+      <c r="A144" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="B136:B141"/>
     <mergeCell ref="A113:A144"/>
@@ -5010,15 +5019,6 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8650307B-591C-4BF2-AAAF-55EFC5B7390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECE2386-F596-4D5D-8C00-9FF90BEFBFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1304,10 +1304,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1439,88 +1439,82 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1937,7 +1931,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
@@ -4622,7 +4616,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="45"/>
+      <c r="A114" s="32"/>
       <c r="B114" s="39"/>
       <c r="C114" s="6" t="s">
         <v>174</v>
@@ -4635,7 +4629,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="45"/>
+      <c r="A115" s="32"/>
       <c r="B115" s="43"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4643,7 +4637,7 @@
       <c r="F115" s="14"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="45"/>
+      <c r="A116" s="32"/>
       <c r="B116" s="42" t="s">
         <v>183</v>
       </c>
@@ -4658,7 +4652,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="45"/>
+      <c r="A117" s="32"/>
       <c r="B117" s="39"/>
       <c r="C117" s="6" t="s">
         <v>181</v>
@@ -4671,7 +4665,7 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="45"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="39"/>
       <c r="C118" s="6" t="s">
         <v>177</v>
@@ -4684,7 +4678,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="45"/>
+      <c r="A119" s="32"/>
       <c r="B119" s="39"/>
       <c r="C119" s="6" t="s">
         <v>179</v>
@@ -4697,7 +4691,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="45"/>
+      <c r="A120" s="32"/>
       <c r="B120" s="39"/>
       <c r="C120" s="6" t="s">
         <v>182</v>
@@ -4710,7 +4704,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="45"/>
+      <c r="A121" s="32"/>
       <c r="B121" s="39"/>
       <c r="C121" s="6" t="s">
         <v>191</v>
@@ -4723,11 +4717,11 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="45"/>
+      <c r="A122" s="32"/>
       <c r="B122" s="39"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="45"/>
+      <c r="A123" s="32"/>
       <c r="B123" s="42" t="s">
         <v>206</v>
       </c>
@@ -4743,7 +4737,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="45"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="39"/>
       <c r="C124" s="6" t="s">
         <v>204</v>
@@ -4756,7 +4750,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="45"/>
+      <c r="A125" s="32"/>
       <c r="B125" s="39"/>
       <c r="C125" s="6" t="s">
         <v>215</v>
@@ -4769,7 +4763,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="45"/>
+      <c r="A126" s="32"/>
       <c r="B126" s="39"/>
       <c r="C126" s="6" t="s">
         <v>205</v>
@@ -4782,7 +4776,7 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="45"/>
+      <c r="A127" s="32"/>
       <c r="B127" s="39"/>
       <c r="C127" s="6" t="s">
         <v>328</v>
@@ -4795,7 +4789,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="45"/>
+      <c r="A128" s="32"/>
       <c r="B128" s="39"/>
       <c r="C128" s="6" t="s">
         <v>352</v>
@@ -4808,7 +4802,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="45"/>
+      <c r="A129" s="32"/>
       <c r="B129" s="39"/>
       <c r="C129" s="6" t="s">
         <v>354</v>
@@ -4821,7 +4815,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="45"/>
+      <c r="A130" s="32"/>
       <c r="B130" s="39"/>
       <c r="C130" s="6" t="s">
         <v>217</v>
@@ -4834,7 +4828,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="45"/>
+      <c r="A131" s="32"/>
       <c r="B131" s="39"/>
       <c r="C131" s="6" t="s">
         <v>221</v>
@@ -4847,7 +4841,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="45"/>
+      <c r="A132" s="32"/>
       <c r="B132" s="39"/>
       <c r="C132" s="6" t="s">
         <v>202</v>
@@ -4860,7 +4854,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="45"/>
+      <c r="A133" s="32"/>
       <c r="B133" s="39"/>
       <c r="C133" s="6" t="s">
         <v>278</v>
@@ -4873,7 +4867,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="45"/>
+      <c r="A134" s="32"/>
       <c r="B134" s="39"/>
       <c r="C134" s="6" t="s">
         <v>281</v>
@@ -4886,11 +4880,11 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="45"/>
+      <c r="A135" s="32"/>
       <c r="B135" s="39"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="45"/>
+      <c r="A136" s="32"/>
       <c r="B136" s="42" t="s">
         <v>222</v>
       </c>
@@ -4906,8 +4900,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="45"/>
-      <c r="B137" s="44"/>
+      <c r="A137" s="32"/>
+      <c r="B137" s="39"/>
       <c r="C137" s="6" t="s">
         <v>330</v>
       </c>
@@ -4919,8 +4913,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="45"/>
-      <c r="B138" s="44"/>
+      <c r="A138" s="32"/>
+      <c r="B138" s="39"/>
       <c r="C138" s="6" t="s">
         <v>225</v>
       </c>
@@ -4932,8 +4926,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="45"/>
-      <c r="B139" s="44"/>
+      <c r="A139" s="32"/>
+      <c r="B139" s="39"/>
       <c r="C139" s="6" t="s">
         <v>282</v>
       </c>
@@ -4945,8 +4939,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="45"/>
-      <c r="B140" s="44"/>
+      <c r="A140" s="32"/>
+      <c r="B140" s="39"/>
       <c r="C140" s="6" t="s">
         <v>284</v>
       </c>
@@ -4958,11 +4952,11 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="45"/>
+      <c r="A141" s="32"/>
       <c r="B141" s="43"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="45"/>
+      <c r="A142" s="32"/>
       <c r="B142" s="42" t="s">
         <v>358</v>
       </c>
@@ -4978,7 +4972,7 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="45"/>
+      <c r="A143" s="32"/>
       <c r="B143" s="39"/>
       <c r="C143" s="6" t="s">
         <v>361</v>
@@ -4991,19 +4985,10 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="45"/>
+      <c r="A144" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="B136:B141"/>
     <mergeCell ref="A113:A144"/>
@@ -5019,6 +5004,15 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECE2386-F596-4D5D-8C00-9FF90BEFBFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F1B08E-E057-4EC5-87F2-82326B8E47CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -882,12 +882,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>CO2-Bereitstellung / Direct Air Capture</t>
   </si>
   <si>
@@ -1167,13 +1161,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1304,10 +1292,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1439,44 +1427,44 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1988,19 +1976,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="32"/>
       <c r="B8" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E8" s="21">
         <v>1.5</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2010,7 +1998,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E9" s="9">
         <v>285.39999999999998</v>
@@ -2026,13 +2014,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" s="9">
         <v>5110</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2042,7 +2030,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E11" s="11">
         <v>0.05</v>
@@ -2058,29 +2046,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E13" s="9">
         <v>1.375</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2090,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E14" s="12">
         <v>25</v>
@@ -2106,7 +2094,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E15" s="15">
         <v>0.08</v>
@@ -2118,13 +2106,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="32"/>
       <c r="B16" s="42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E16" s="17">
         <v>3.7</v>
@@ -2140,13 +2128,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2156,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2172,7 +2160,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E19" s="11">
         <v>0.02</v>
@@ -2188,7 +2176,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E20" s="11">
         <v>20</v>
@@ -2204,7 +2192,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E21" s="15">
         <v>0.05</v>
@@ -2216,35 +2204,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="32"/>
       <c r="B22" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E22" s="9">
         <v>0.5</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="32"/>
       <c r="B23" s="35"/>
       <c r="C23" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E23" s="9">
         <v>1.75</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2254,13 +2242,13 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E24" s="9">
         <v>7000</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2270,7 +2258,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" s="11">
         <v>0.05</v>
@@ -2286,7 +2274,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" s="12">
         <v>15</v>
@@ -2302,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E27" s="11">
         <v>7.0000000000000007E-2</v>
@@ -2446,19 +2434,19 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="32"/>
       <c r="B36" s="37" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E36" s="13">
         <v>2.83</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2468,7 +2456,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E37" s="11">
         <v>0.03</v>
@@ -2484,7 +2472,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E38" s="12">
         <v>30</v>
@@ -2500,7 +2488,7 @@
         <v>20</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E39" s="11">
         <v>7.3999999999999999E-4</v>
@@ -2516,7 +2504,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E40" s="11">
         <v>0.98</v>
@@ -2532,7 +2520,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E41" s="11">
         <v>0.98</v>
@@ -2548,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E42" s="11">
         <v>0.05</v>
@@ -2564,7 +2552,7 @@
         <v>88</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E43" s="15">
         <v>0</v>
@@ -2998,7 +2986,7 @@
         <v>78</v>
       </c>
       <c r="E69" s="27">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="26" t="s">
         <v>19</v>
@@ -3007,19 +2995,19 @@
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="32"/>
       <c r="B70" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>317</v>
-      </c>
       <c r="E70" s="11">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3043,19 +3031,19 @@
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E72" s="19">
         <v>-0.6</v>
       </c>
       <c r="F72" s="18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3082,7 +3070,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
@@ -3252,13 +3240,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="32"/>
       <c r="B12" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="16" t="s">
@@ -3269,14 +3257,14 @@
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3286,7 +3274,7 @@
         <v>139</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
@@ -3297,14 +3285,14 @@
       <c r="A15" s="32"/>
       <c r="B15" s="39"/>
       <c r="C15" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3314,7 +3302,7 @@
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="6" t="s">
@@ -3328,7 +3316,7 @@
         <v>141</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="6" t="s">
@@ -3342,7 +3330,7 @@
         <v>155</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="6" t="s">
@@ -3356,7 +3344,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="6" t="s">
@@ -3370,7 +3358,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="6" t="s">
@@ -3384,7 +3372,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
@@ -3402,17 +3390,17 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="32"/>
       <c r="B23" s="42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3410,7 @@
         <v>107</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="6" t="s">
@@ -3436,25 +3424,25 @@
         <v>84</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="32"/>
       <c r="B26" s="39"/>
       <c r="C26" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3464,7 +3452,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="6" t="s">
@@ -3478,7 +3466,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="6" t="s">
@@ -3492,7 +3480,7 @@
         <v>196</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="6" t="s">
@@ -3506,7 +3494,7 @@
         <v>167</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="6" t="s">
@@ -3520,7 +3508,7 @@
         <v>188</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="6" t="s">
@@ -3538,13 +3526,13 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="32"/>
       <c r="B33" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="6" t="s">
@@ -3558,7 +3546,7 @@
         <v>107</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="6" t="s">
@@ -3572,7 +3560,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="6" t="s">
@@ -3583,28 +3571,28 @@
       <c r="A36" s="32"/>
       <c r="B36" s="35"/>
       <c r="C36" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="32"/>
       <c r="B37" s="35"/>
       <c r="C37" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -3614,7 +3602,7 @@
         <v>141</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="6" t="s">
@@ -3628,7 +3616,7 @@
         <v>155</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="6" t="s">
@@ -3642,7 +3630,7 @@
         <v>196</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="6" t="s">
@@ -3656,7 +3644,7 @@
         <v>167</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="6" t="s">
@@ -3670,7 +3658,7 @@
         <v>188</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="6" t="s">
@@ -3697,7 +3685,7 @@
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -3711,7 +3699,7 @@
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3823,17 +3811,17 @@
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="32"/>
       <c r="B54" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>113</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -3843,11 +3831,11 @@
         <v>111</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3857,11 +3845,11 @@
         <v>135</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3871,11 +3859,11 @@
         <v>136</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3885,7 +3873,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="6" t="s">
@@ -3899,7 +3887,7 @@
         <v>155</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="6" t="s">
@@ -3913,7 +3901,7 @@
         <v>196</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="6" t="s">
@@ -3927,7 +3915,7 @@
         <v>167</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="6" t="s">
@@ -3941,7 +3929,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="6" t="s">
@@ -4440,10 +4428,10 @@
       <c r="A100" s="32"/>
       <c r="B100" s="39"/>
       <c r="C100" s="6" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="6" t="s">
@@ -4452,200 +4440,198 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
-      <c r="B101" s="39"/>
-      <c r="C101" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B101" s="43"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="14"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="32"/>
-      <c r="B102" s="43"/>
-      <c r="C102" s="14"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="14"/>
+      <c r="B102" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E102" s="11"/>
+      <c r="F102" s="6" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="32"/>
-      <c r="B103" s="42" t="s">
-        <v>319</v>
-      </c>
+      <c r="B103" s="39"/>
       <c r="C103" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D103" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="E103" s="11"/>
       <c r="F103" s="6" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="32"/>
-      <c r="B104" s="39"/>
-      <c r="C104" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>322</v>
-      </c>
+      <c r="B104" s="43"/>
       <c r="E104" s="11"/>
-      <c r="F104" s="6" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="32"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="6" t="s">
-        <v>149</v>
+      <c r="B105" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="17"/>
+      <c r="F105" s="16" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="32"/>
-      <c r="B106" s="43"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="E106" s="11"/>
+      <c r="F106" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="32"/>
-      <c r="B107" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C107" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D107" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E107" s="17"/>
-      <c r="F107" s="16" t="s">
-        <v>132</v>
-      </c>
+      <c r="B107" s="43"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="14"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="32"/>
-      <c r="B108" s="39"/>
+      <c r="B108" s="42" t="s">
+        <v>272</v>
+      </c>
       <c r="C108" s="6" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="6" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="32"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="14"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="32"/>
-      <c r="B110" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="C110" s="6" t="s">
+      <c r="B109" s="39"/>
+      <c r="C109" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D110" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="6" t="s">
-        <v>262</v>
-      </c>
+      <c r="D109" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E109" s="11"/>
+      <c r="F109" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="33"/>
+      <c r="B110" s="40"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="18"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="32"/>
-      <c r="B111" s="39"/>
-      <c r="C111" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E111" s="11"/>
-      <c r="F111" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="33"/>
-      <c r="B112" s="40"/>
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="18"/>
+      <c r="A111" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="32"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B113" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7" t="s">
-        <v>140</v>
-      </c>
+      <c r="A113" s="32"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="32"/>
-      <c r="B114" s="39"/>
+      <c r="B114" s="42" t="s">
+        <v>183</v>
+      </c>
       <c r="C114" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="32"/>
-      <c r="B115" s="43"/>
-      <c r="C115" s="14"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="32"/>
-      <c r="B116" s="42" t="s">
-        <v>183</v>
-      </c>
+      <c r="B116" s="39"/>
       <c r="C116" s="6" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>149</v>
@@ -4655,10 +4641,10 @@
       <c r="A117" s="32"/>
       <c r="B117" s="39"/>
       <c r="C117" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>327</v>
+        <v>178</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>149</v>
@@ -4668,10 +4654,10 @@
       <c r="A118" s="32"/>
       <c r="B118" s="39"/>
       <c r="C118" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>149</v>
@@ -4681,10 +4667,10 @@
       <c r="A119" s="32"/>
       <c r="B119" s="39"/>
       <c r="C119" s="6" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>149</v>
@@ -4693,57 +4679,57 @@
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="32"/>
       <c r="B120" s="39"/>
-      <c r="C120" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="32"/>
-      <c r="B121" s="39"/>
-      <c r="C121" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>149</v>
+      <c r="B121" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" s="16"/>
+      <c r="F121" s="16" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="32"/>
       <c r="B122" s="39"/>
+      <c r="C122" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="32"/>
-      <c r="B123" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E123" s="16"/>
-      <c r="F123" s="16" t="s">
-        <v>208</v>
+      <c r="B123" s="39"/>
+      <c r="C123" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="32"/>
       <c r="B124" s="39"/>
       <c r="C124" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>208</v>
@@ -4753,88 +4739,88 @@
       <c r="A125" s="32"/>
       <c r="B125" s="39"/>
       <c r="C125" s="6" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>214</v>
+        <v>325</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>219</v>
+        <v>328</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="32"/>
       <c r="B126" s="39"/>
       <c r="C126" s="6" t="s">
-        <v>205</v>
+        <v>348</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="32"/>
       <c r="B127" s="39"/>
       <c r="C127" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F127" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="32"/>
       <c r="B128" s="39"/>
       <c r="C128" s="6" t="s">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>353</v>
+        <v>216</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>332</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="32"/>
       <c r="B129" s="39"/>
       <c r="C129" s="6" t="s">
-        <v>354</v>
+        <v>221</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>355</v>
+        <v>211</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="32"/>
       <c r="B130" s="39"/>
       <c r="C130" s="6" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="32"/>
       <c r="B131" s="39"/>
       <c r="C131" s="6" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>212</v>
@@ -4844,166 +4830,125 @@
       <c r="A132" s="32"/>
       <c r="B132" s="39"/>
       <c r="C132" s="6" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="32"/>
       <c r="B133" s="39"/>
-      <c r="C133" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="32"/>
-      <c r="B134" s="39"/>
-      <c r="C134" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>213</v>
+      <c r="B134" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="E134" s="16"/>
+      <c r="F134" s="16" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="32"/>
       <c r="B135" s="39"/>
+      <c r="C135" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="32"/>
-      <c r="B136" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16" t="s">
-        <v>208</v>
+      <c r="B136" s="39"/>
+      <c r="C136" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="32"/>
       <c r="B137" s="39"/>
       <c r="C137" s="6" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>331</v>
+        <v>281</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="32"/>
       <c r="B138" s="39"/>
       <c r="C138" s="6" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="32"/>
-      <c r="B139" s="39"/>
-      <c r="C139" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>212</v>
-      </c>
+      <c r="B139" s="43"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="32"/>
-      <c r="B140" s="39"/>
-      <c r="C140" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>213</v>
+      <c r="B140" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="32"/>
-      <c r="B141" s="43"/>
+      <c r="B141" s="39"/>
+      <c r="C141" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="32"/>
-      <c r="B142" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="C142" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="E142" s="16"/>
-      <c r="F142" s="16" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="32"/>
-      <c r="B143" s="39"/>
-      <c r="C143" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A113:A144"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B116:B122"/>
-    <mergeCell ref="B123:B135"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="A2:A43"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -5013,6 +4958,21 @@
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="B44:B53"/>
     <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B134:B139"/>
+    <mergeCell ref="A111:A142"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B114:B120"/>
+    <mergeCell ref="B121:B133"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A110"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B99:B101"/>
+    <mergeCell ref="B102:B104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
